--- a/refs/heads/main/StructureDefinition-CondicionLE1.xlsx
+++ b/refs/heads/main/StructureDefinition-CondicionLE1.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-CondicionLE1.xlsx
+++ b/refs/heads/main/StructureDefinition-CondicionLE1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -913,13 +913,13 @@
     <t>Condition.code.coding.system</t>
   </si>
   <si>
-    <t>http://id.who.int/icd/release/11/mms</t>
-  </si>
-  <si>
     <t>Condition.code.coding.version</t>
   </si>
   <si>
     <t>Condition.code.coding.code</t>
+  </si>
+  <si>
+    <t>http://minsal.cl/listaespera/ValueSet/VSTipoCodDiagnostica</t>
   </si>
   <si>
     <t>Condition.code.coding.display</t>
@@ -965,7 +965,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PacienteLE)
 </t>
   </si>
   <si>
@@ -1650,7 +1650,7 @@
     <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="85.23828125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="50.7109375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="55.6171875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>84</v>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>84</v>
@@ -5470,7 +5470,7 @@
         <v>74</v>
       </c>
       <c r="R33" t="s" s="2">
-        <v>287</v>
+        <v>74</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>74</v>
@@ -5544,7 +5544,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5661,7 +5661,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5719,13 +5719,11 @@
         <v>74</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="X35" s="2"/>
       <c r="Y35" t="s" s="2">
-        <v>74</v>
+        <v>289</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>74</v>
@@ -5786,7 +5784,7 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>84</v>
